--- a/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица КИ ЗПФ (Боярко с 14,10,26).xlsx
+++ b/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица КИ ЗПФ (Боярко с 14,10,26).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uaer4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\матрицы ПОКОМ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E2640D-FE20-42DB-9F54-63540529E8AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0A9F55-1172-45F5-B863-D9E2C3A21931}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4431,7 +4431,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4499,13 +4499,14 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -10679,14 +10680,14 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="34" t="s">
         <v>369</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33" t="s">
+      <c r="D4" s="34"/>
+      <c r="E4" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="F4" s="33"/>
+      <c r="F4" s="34"/>
       <c r="G4" s="24" t="s">
         <v>1422</v>
       </c>
@@ -10814,14 +10815,14 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>369</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34" t="s">
+      <c r="D4" s="35"/>
+      <c r="E4" s="35" t="s">
         <v>370</v>
       </c>
-      <c r="F4" s="34"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="24" t="s">
         <v>1422</v>
       </c>
@@ -10854,7 +10855,7 @@
       <c r="G5" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="33" t="s">
         <v>1426</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -10863,7 +10864,7 @@
       <c r="J5" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="K5" s="35" t="s">
+      <c r="K5" s="33" t="s">
         <v>1427</v>
       </c>
     </row>
@@ -10883,7 +10884,7 @@
       <c r="G6" s="32" t="s">
         <v>1427</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="36" t="s">
         <v>1429</v>
       </c>
       <c r="I6" s="32" t="s">
@@ -10892,7 +10893,7 @@
       <c r="J6" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="K6" s="35" t="s">
+      <c r="K6" s="33" t="s">
         <v>1428</v>
       </c>
     </row>
